--- a/events/Moscow_2012_WC/Moscow_2012_WC_Results.xlsx
+++ b/events/Moscow_2012_WC/Moscow_2012_WC_Results.xlsx
@@ -19906,11 +19906,6 @@
           <t>36175</t>
         </is>
       </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>84718</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -28340,11 +28335,6 @@
       <c r="R432" t="inlineStr">
         <is>
           <t>36175</t>
-        </is>
-      </c>
-      <c r="S432" t="inlineStr">
-        <is>
-          <t>84718</t>
         </is>
       </c>
     </row>
@@ -34347,7 +34337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35409,61 +35399,61 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>84718</t>
+          <t>36165</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nikolay</t>
+          <t>Natalia</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lipkin</t>
+          <t>Lobova</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>36154</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Kirill</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lobova</t>
+          <t>Luchkin</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>36154</t>
+          <t>36147</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kirill</t>
+          <t>Ilya</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Luchkin</t>
+          <t>Medvedev</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -35475,17 +35465,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ilya</t>
+          <t>Maxim</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Medvedev</t>
+          <t>Molochkov</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -35497,17 +35487,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>36141</t>
+          <t>42389</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Maxim</t>
+          <t>Ruslan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Molochkov</t>
+          <t>Moltaev</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -35519,17 +35509,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>42389</t>
+          <t>36731</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ruslan</t>
+          <t>Tamerlan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Moltaev</t>
+          <t>Mustafayev</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -35541,17 +35531,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>36731</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tamerlan</t>
+          <t>Ignas</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mustafayev</t>
+          <t>Navakauskas</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -35563,17 +35553,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ignas</t>
+          <t>Ricardas</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Navakauskas</t>
+          <t>Nekriosius</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -35585,61 +35575,61 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>45837</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ricardas</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nekriosius</t>
+          <t>Nicholls</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>36140</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nicholls</t>
+          <t>Nikolaev</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>36140</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nikolaev</t>
+          <t>Oldershaw</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -35651,17 +35641,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Andrej</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oldershaw</t>
+          <t>Olijnik</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -35673,17 +35663,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>36635</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Andrej</t>
+          <t>Ronilson Matias De</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Olijnik</t>
+          <t>Oliveira</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -35695,17 +35685,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>36635</t>
+          <t>36499</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ronilson Matias De</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oliveira</t>
+          <t>Oropeza</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -35717,17 +35707,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>64876</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Fortunato</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oropeza</t>
+          <t>Pacavira</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -35739,17 +35729,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>64876</t>
+          <t>36495</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fortunato</t>
+          <t>Edwar</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pacavira</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -35761,17 +35751,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>36495</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Edwar</t>
+          <t>Aleksandr</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Parol</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -35783,17 +35773,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>36347</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>Dmitry</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Parol</t>
+          <t>Petrov</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -35805,12 +35795,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>36347</t>
+          <t>36163</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dmitry</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -35827,12 +35817,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>36163</t>
+          <t>42569</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Vladimir</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -35849,61 +35839,61 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>52178</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vladimir</t>
+          <t>Yekaterina</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Petrov</t>
+          <t>Podstavochkina</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>52178</t>
+          <t>36150</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Yekaterina</t>
+          <t>Vasily</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Podstavochkina</t>
+          <t>Pogreban</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>36150</t>
+          <t>35549</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vasily</t>
+          <t>Jaroslav</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pogreban</t>
+          <t>Radon</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -35915,17 +35905,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>35549</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jaroslav</t>
+          <t>Jose Giovanny</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Radon</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -35937,17 +35927,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>36496</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jose Giovanny</t>
+          <t>Ronny</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Ratia</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -35959,17 +35949,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>36496</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ronny</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ratia</t>
+          <t>Rendschmidt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -35981,17 +35971,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>36666</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Aleksejs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rendschmidt</t>
+          <t>Rumjancevs</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -36003,17 +35993,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>36593</t>
+          <t>42113</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Aleksejs</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rumjancevs</t>
+          <t>Rusu</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -36025,17 +36015,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>42113</t>
+          <t>36148</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rusu</t>
+          <t>Ryakhov</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -36047,39 +36037,39 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>36148</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Yuliana</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ryakhov</t>
+          <t>Salakhova</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>36170</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Yuliana</t>
+          <t>Zulmarys</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salakhova</t>
+          <t>Sanchez</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -36091,39 +36081,39 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>36180</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Zulmarys</t>
+          <t>Kirill</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sanchez</t>
+          <t>Shamshurin</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>36180</t>
+          <t>36474</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kirill</t>
+          <t>Dongjin</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Shamshurin</t>
+          <t>Shin</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -36135,61 +36125,61 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>56337</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dongjin</t>
+          <t>Ekaterina</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Shin</t>
+          <t>Shubina</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>56337</t>
+          <t>36792</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ekaterina</t>
+          <t>Jevgenij</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Shubina</t>
+          <t>Shuklin</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jevgenij</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Shuklin</t>
+          <t>Siemionowski</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -36201,17 +36191,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>35858</t>
+          <t>36634</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Erlon De Souza</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Siemionowski</t>
+          <t>Silva</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -36223,17 +36213,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>36634</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Erlon De Souza</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Silva</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -36245,17 +36235,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>36667</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kai</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Spenner</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -36267,17 +36257,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>36667</t>
+          <t>45793</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Kai</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spenner</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -36289,17 +36279,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>46101</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Johnnathan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Tafra</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -36311,17 +36301,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>46101</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Johnnathan</t>
+          <t>Daniil</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tafra</t>
+          <t>Teterev</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -36333,17 +36323,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>64637</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Daniil</t>
+          <t>Leonid</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Teterev</t>
+          <t>Tilsh</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -36355,17 +36345,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>52225</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Leonid</t>
+          <t>Artur</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tilsh</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -36377,17 +36367,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Alvaro</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Torres</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -36399,17 +36389,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>46419</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Alvaro</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Torres</t>
+          <t>Van Koeverden</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -36421,17 +36411,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Van Koeverden</t>
+          <t>Vandrey</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -36443,17 +36433,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>36672</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Vandrey</t>
+          <t>Vasilyev</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -36465,17 +36455,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>36151</t>
+          <t>56383</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Serghei</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Vasilyev</t>
+          <t>Vihrov</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -36487,17 +36477,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>56383</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Serghei</t>
+          <t>Alexandr</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Vihrov</t>
+          <t>Yemelyanov</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -36509,12 +36499,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>42562</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Alexandr</t>
+          <t>Mikhail</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -36531,12 +36521,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>42562</t>
+          <t>42561</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mikhail</t>
+          <t>Sergey</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -36553,12 +36543,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>42563</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sergey</t>
+          <t>Timofey</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -36575,17 +36565,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>42563</t>
+          <t>36149</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Timofey</t>
+          <t>Vitaly</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Yemelyanov</t>
+          <t>Yurchenko</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -36597,17 +36587,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>36149</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Vitaly</t>
+          <t>Jost</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Yurchenko</t>
+          <t>Zakrajsek</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -36619,17 +36609,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>36152</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jost</t>
+          <t>Oleg</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Zakrajsek</t>
+          <t>Zhestkov</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -36641,17 +36631,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>36152</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Oleg</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Zhestkov</t>
+          <t>ANOSHKIN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -36663,17 +36653,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>36146</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Ilia</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ANOSHKIN</t>
+          <t>SHTOKALOV</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -36685,17 +36675,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>36159</t>
+          <t>36160</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ilia</t>
+          <t>Ilya</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SHTOKALOV</t>
+          <t>PERVUKHIN</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -36707,17 +36697,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>36160</t>
+          <t>36161</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ilya</t>
+          <t>Alexey</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PERVUKHIN</t>
+          <t>KOROVASHKOV</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -36729,86 +36719,64 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>36161</t>
+          <t>36164</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Alexey</t>
+          <t>Natalia</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KOROVASHKOV</t>
+          <t>PODOLSKAIA</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>36164</t>
+          <t>36175</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Viktor</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PODOLSKAIA</t>
+          <t>MELANTEV</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>36175</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Viktor</t>
+          <t>Aleksey</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MELANTEV</t>
+          <t>MOCHALOV</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>52228</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Aleksey</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>MOCHALOV</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Moscow_2012_WC/Moscow_2012_WC_Results.xlsx
+++ b/events/Moscow_2012_WC/Moscow_2012_WC_Results.xlsx
@@ -3066,6 +3066,11 @@
           <t>00:04:17.744</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>52787</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4866,6 +4871,11 @@
           <t>00:04:26.136</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>52787</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -12312,6 +12322,11 @@
           <t>00:05:32.376</t>
         </is>
       </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>52787</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -14322,6 +14337,11 @@
           <t>00:01:52.950</t>
         </is>
       </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="T216" t="inlineStr">
         <is>
           <t>36164</t>
@@ -15206,6 +15226,11 @@
           <t>175207</t>
         </is>
       </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>52787</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -17373,6 +17398,11 @@
           <t>00:00:44.568</t>
         </is>
       </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>52787</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -19461,6 +19491,11 @@
           <t>00:00:37.724</t>
         </is>
       </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>45847</t>
+        </is>
+      </c>
       <c r="S295" t="inlineStr">
         <is>
           <t>46764</t>
@@ -22470,6 +22505,11 @@
           <t>00:00:46.326</t>
         </is>
       </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>52787</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -26873,6 +26913,11 @@
           <t>00:00:42.643</t>
         </is>
       </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>52787</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -27729,6 +27774,11 @@
           <t>46764</t>
         </is>
       </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>45847</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -33026,6 +33076,11 @@
       <c r="P503" t="inlineStr">
         <is>
           <t>00:23:44.721</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>52787</t>
         </is>
       </c>
     </row>
@@ -34337,7 +34392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36782,6 +36837,72 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>52787</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Adel</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Mojallalimoghaddam Foumani</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Anyshina</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>45847</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Phillip</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
